--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-12-2025.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>£31.88</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>£32.98</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-12-2025.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£9.60</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.10</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£24.38</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£26.35</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£31.88</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1615,24 +1615,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£31.00</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£30.4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>£30.45</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£31.00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£30.4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£30.45</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>£30.27</t>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£32.98</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
